--- a/data/ams_weekly_data/White_Mulberry/ads_report_week30.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week30.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +19,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +36,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +44,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,42 +419,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -1078,7 +1067,7 @@
         <v>233</v>
       </c>
       <c r="F23" t="n">
-        <v>17783</v>
+        <v>17782</v>
       </c>
       <c r="G23" t="n">
         <v>10168.64</v>
@@ -1280,7 +1269,7 @@
         <v>11858.49</v>
       </c>
       <c r="H30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
@@ -1610,7 +1599,7 @@
         <v>312</v>
       </c>
       <c r="F42" t="n">
-        <v>105044</v>
+        <v>105042</v>
       </c>
       <c r="G42" t="n">
         <v>5082.21</v>
@@ -2338,7 +2327,7 @@
         <v>77</v>
       </c>
       <c r="F68" t="n">
-        <v>19649</v>
+        <v>19648</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -3402,7 +3391,7 @@
         <v>54</v>
       </c>
       <c r="F106" t="n">
-        <v>4233</v>
+        <v>4231</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3906,7 +3895,7 @@
         <v>144</v>
       </c>
       <c r="F124" t="n">
-        <v>47457</v>
+        <v>47456</v>
       </c>
       <c r="G124" t="n">
         <v>8470.35</v>
@@ -4102,7 +4091,7 @@
         <v>89</v>
       </c>
       <c r="F131" t="n">
-        <v>14804</v>
+        <v>14803</v>
       </c>
       <c r="G131" t="n">
         <v>1015.26</v>
@@ -4186,7 +4175,7 @@
         <v>122</v>
       </c>
       <c r="F134" t="n">
-        <v>42966</v>
+        <v>42965</v>
       </c>
       <c r="G134" t="n">
         <v>1524.58</v>
@@ -4214,7 +4203,7 @@
         <v>35</v>
       </c>
       <c r="F135" t="n">
-        <v>15059</v>
+        <v>15057</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -4294,42 +4283,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -5145,6 +5134,628 @@
       </c>
       <c r="H30" t="n">
         <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Portfolio name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Campaign Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Advertised ASIN</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Impressions</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Clicks</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>14 Day Total Sales (₹)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>14 Day Total Units (#)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>B0CPFS24ML</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>12280</v>
+      </c>
+      <c r="E2" t="n">
+        <v>376</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1262.43</v>
+      </c>
+      <c r="G2" t="n">
+        <v>14574.58</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SB-L shape-Multi Asin- KT- phrase</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>B0BFW59TRG</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>41106</v>
+      </c>
+      <c r="E3" t="n">
+        <v>240</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1894.26</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7031.36</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>WM- SBV- Monitor Arm- B0DB5VG39T - PT</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>17655</v>
+      </c>
+      <c r="E4" t="n">
+        <v>122</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1462.97</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>WM- SBV- Monitor Arm- B0DB5VG39T - Phrase</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>31306</v>
+      </c>
+      <c r="E5" t="n">
+        <v>124</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1582.77</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2329.66</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>WM- SBV- Monitor Arm- B0DB5VG39T- Exact</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>29294</v>
+      </c>
+      <c r="E6" t="n">
+        <v>75</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1382.11</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>WM- SBV- Monitor Arm- Product Collection- Phrase</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>B0DB5YTQZV</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>9691</v>
+      </c>
+      <c r="E7" t="n">
+        <v>56</v>
+      </c>
+      <c r="F7" t="n">
+        <v>963.0599999999999</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1694.06</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>28</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>5.926666666666667</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>B0DB5VVPSB</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>28</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5.926666666666667</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>B0DB5W4TCP</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>28</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5.926666666666667</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>B0DB5YTQZV</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>28</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>5.926666666666667</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>28</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5.926666666666667</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>28</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5.926666666666667</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>19171</v>
+      </c>
+      <c r="E14" t="n">
+        <v>175</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2198.106414187307</v>
+      </c>
+      <c r="G14" t="n">
+        <v>13302.11529039575</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>B0FN4JG97R</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>7835</v>
+      </c>
+      <c r="E15" t="n">
+        <v>72</v>
+      </c>
+      <c r="F15" t="n">
+        <v>898.2735858126931</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5436.014709604247</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>20234</v>
+      </c>
+      <c r="E16" t="n">
+        <v>220</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2668.86</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-KT-SBV</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>31928</v>
+      </c>
+      <c r="E17" t="n">
+        <v>206</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3255.77</v>
+      </c>
+      <c r="G17" t="n">
+        <v>9403.389999999999</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>White Mulberry-Monitor Arm-Collective- SB - Phrase</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>28444</v>
+      </c>
+      <c r="E18" t="n">
+        <v>48</v>
+      </c>
+      <c r="F18" t="n">
+        <v>577.1900000000001</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5252.54</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week30.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week30.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -36,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -44,12 +47,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -419,42 +431,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -1269,7 +1281,7 @@
         <v>11858.49</v>
       </c>
       <c r="H30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
@@ -4283,42 +4295,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -5151,47 +5163,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
